--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129881075</v>
+        <v>129884170</v>
       </c>
       <c r="B2" t="n">
-        <v>97651</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>277618</v>
+        <v>277684</v>
       </c>
       <c r="R2" t="n">
-        <v>6532311</v>
+        <v>6532283</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,42 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129884170</v>
+        <v>129881075</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>97661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>277684</v>
+        <v>277618</v>
       </c>
       <c r="R3" t="n">
-        <v>6532283</v>
+        <v>6532311</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>129881183</v>
       </c>
       <c r="B4" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129881125</v>
       </c>
       <c r="B5" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129880982</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>129881931</v>
       </c>
       <c r="B7" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884170</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129881075</v>
       </c>
       <c r="B3" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129881183</v>
       </c>
       <c r="B4" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129881125</v>
       </c>
       <c r="B5" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129880982</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>129881931</v>
       </c>
       <c r="B7" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129884170</v>
+        <v>129881075</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>97665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>277684</v>
+        <v>277618</v>
       </c>
       <c r="R2" t="n">
-        <v>6532283</v>
+        <v>6532311</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +786,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129881075</v>
+        <v>129884170</v>
       </c>
       <c r="B3" t="n">
-        <v>97665</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>277618</v>
+        <v>277684</v>
       </c>
       <c r="R3" t="n">
-        <v>6532311</v>
+        <v>6532283</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129881075</v>
+        <v>129884170</v>
       </c>
       <c r="B2" t="n">
-        <v>97665</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>277618</v>
+        <v>277684</v>
       </c>
       <c r="R2" t="n">
-        <v>6532311</v>
+        <v>6532283</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,42 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129884170</v>
+        <v>129881075</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>277684</v>
+        <v>277618</v>
       </c>
       <c r="R3" t="n">
-        <v>6532283</v>
+        <v>6532311</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>129881183</v>
       </c>
       <c r="B4" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129881125</v>
       </c>
       <c r="B5" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129880982</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>129881931</v>
       </c>
       <c r="B7" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884170</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129881075</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129881183</v>
       </c>
       <c r="B4" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129881125</v>
       </c>
       <c r="B5" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129880982</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>129881931</v>
       </c>
       <c r="B7" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884170</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129881075</v>
       </c>
       <c r="B3" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129881183</v>
       </c>
       <c r="B4" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129881125</v>
       </c>
       <c r="B5" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129880982</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>129881931</v>
       </c>
       <c r="B7" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884170</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129881075</v>
       </c>
       <c r="B3" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129881183</v>
       </c>
       <c r="B4" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129881125</v>
       </c>
       <c r="B5" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129880982</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>129881931</v>
       </c>
       <c r="B7" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884170</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129881075</v>
       </c>
       <c r="B3" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129881183</v>
       </c>
       <c r="B4" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129881125</v>
       </c>
       <c r="B5" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129880982</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>129881931</v>
       </c>
       <c r="B7" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6043-2024 artfynd.xlsx
+++ b/artfynd/A 6043-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880982</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881384</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129884170</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881125</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881183</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881931</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,8 +1499,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>